--- a/role-expectations/職階別の期待職能.xlsx
+++ b/role-expectations/職階別の期待職能.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>パートナー</t>
+          <t>（執行）社員</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">

--- a/role-expectations/職階別の期待職能.xlsx
+++ b/role-expectations/職階別の期待職能.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="54" customHeight="1">
+    <row r="3" ht="52" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>EP</t>
@@ -687,7 +687,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>3,516〜3,767万円</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -711,8 +711,7 @@
         <is>
           <t>(1)労働分配率43%（部下の売上10%＆メンバーの売上5%計上）
 (2)15名以上の組織を運営できる【仮】
-(3)年商3,000万円規模の新サービス・新拠点を立ち上げた経験がある【仮】
-(4)期待売上高（3,516万円以上）を達成している</t>
+(3)年商3,000万円規模の新サービス・新拠点を立ち上げた経験がある【仮】</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -752,7 +751,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>3,140〜3,391万円</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -821,7 +820,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2,763〜3,014万円</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -890,7 +889,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>2,386〜2,637万円</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/role-expectations/職階別の期待職能.xlsx
+++ b/role-expectations/職階別の期待職能.xlsx
@@ -1121,7 +1121,7 @@
           <t>＜自分で回し切る個人＞
 (1)指示を待たずに自分の担当を回し切り、判断に迷う点だけを上司に上げられる人
 (2)失敗をフィードバックと捉え、挑戦できる人
-(3)質の良い提案書を作成し、周りの人を説得するプランを立案したことがある人</t>
+(3)※工事中※</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">

--- a/role-expectations/職階別の期待職能.xlsx
+++ b/role-expectations/職階別の期待職能.xlsx
@@ -709,7 +709,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>(1)労働分配率43%（部下の売上10%＆メンバーの売上5%計上）
+          <t>(1)給与総額／期待売上高＝50%（部下の売上10%＆メンバーの売上5%計上）
 (2)15名以上の組織を運営できる【仮】
 (3)年商3,000万円規模の新サービス・新拠点を立ち上げた経験がある【仮】</t>
         </is>
@@ -777,7 +777,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>(1)労働分配率43%（部下の売上10%＆メンバーの売上5%計上）
+          <t>(1)給与総額／期待売上高＝50%（部下の売上10%＆メンバーの売上5%計上）
 (2)10名以上の組織を運営できる【仮】
 (3)代表から経営者代理としての信頼を得ている
 (4)数年後のビジョンを明確にして、組織によい刺激を与えている
@@ -847,7 +847,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>(1)労働分配率43%（部下の売上10%計上）
+          <t>(1)給与総額／期待売上高＝50%（部下の売上10%計上）
 (2)担当領域の予算を自ら策定し、期中の軌道修正を含めて達成できる
 (3)ゼロから業務を企画して組織化・収益化する力を有している
 (4)6名以上の組織を運営できる【仮】</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>(1)労働分配率43%（部下の売上10%計上）
+          <t>(1)給与総額／期待売上高＝50%（部下の売上10%計上）
 (2)6名以上の組織（拠点・部門）を運営できる【仮】
 (3)担当拠点の財務状況を把握し、単月黒字を達成できている
 (4)自らの専門領域において、部長を率いて自らで判断ができる</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>(1)労働分配率43%（部下の売上10%計上）
+          <t>(1)給与総額／期待売上高＝50%（部下の売上10%計上）
 (2)他チームとの共同案件を主導し、収益化できている
 (3)繁忙期の応援・引き継ぎをチーム間で設計し、特定の個人に負荷が偏らない状態を作れる
 (4)複数チーム（計6名以上）に影響を及ぼす立場にある【仮】</t>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>(1)労働分配率43%（部下の売上10%計上）
+          <t>(1)給与総額／期待売上高＝50%（部下の売上10%計上）
 (2)3名以上の組織を運営できる【仮】
 (3)チームの担当関与先の月次巡回監査・決算申告を、期限管理を含めチームで完結できる
 (4)部下一人ひとりの担当先と負荷を把握し、期中で組み替えられる</t>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>(1)労働分配率43%
+          <t>(1)給与総額／期待売上高＝50%
 (2)決算・申告を単独で完結し、関与先へ説明できる
 (3)トレーナーとして担当職（S）を指導できる
 (4)担当先からの一次照会を、上司を介さず自ら回答できる</t>
@@ -1200,7 +1200,7 @@
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>【仮】
-(1)労働分配率43%
+(1)給与総額／期待売上高＝50%
 (2)月次巡回監査を担当先について自ら実施し、期限内に完了できる
 (3)教わった手順を、次からは自分だけで再現できる</t>
         </is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>(1)期待売上高・労働分配率は問わない（賞与は在籍月数按分）
+          <t>(1)期待売上高・給与総額比率は問わない（賞与は在籍月数按分）
 (2)担当補助として、指示された作業を期限内に完了できる</t>
         </is>
       </c>
@@ -1322,7 +1322,7 @@
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>※4.労働分配率は、半年間の粗利と自分の給与を比較して計算。新卒の給与は12ヶ月、中途採用の給与は6ヶ月分は計算上考慮しない。</t>
+          <t>※4.給与総額比率＝給与総額÷期待売上高。基準値は50%。新卒の給与は12ヶ月、中途採用の給与は6ヶ月分は計算上考慮しない。</t>
         </is>
       </c>
     </row>
